--- a/data/trans_orig/RUIDO_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Estudios-trans_orig.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>453</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20192</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>26916</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>31453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47061</t>
+          <t>46777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56871</t>
+          <t>56876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -2577,12 +2577,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>820</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>501</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20833</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27629</t>
+          <t>26214</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>376</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>790</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24933</t>
+          <t>24345</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>38071</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44047</t>
+          <t>47084</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33563</t>
+          <t>34249</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64747</t>
+          <t>64317</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>164579</t>
+          <t>165190</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191395</t>
+          <t>191144</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>175188</t>
+          <t>175995</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>205185</t>
+          <t>206168</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>351033</t>
+          <t>348883</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>391515</t>
+          <t>392450</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>474</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>501</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>24061</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>21337</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24389</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>41063</t>
+          <t>40276</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>47266</t>
+          <t>46711</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>61185</t>
+          <t>60717</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>57621</t>
+          <t>57976</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>73845</t>
+          <t>73623</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>110171</t>
+          <t>109394</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>131072</t>
+          <t>131386</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>950</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11821</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>30769</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>13933</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>9821</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>23813</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>29140</t>
+          <t>28897</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>51755</t>
+          <t>51151</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>28146</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>49190</t>
+          <t>48967</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>32627</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>63226</t>
+          <t>60677</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>67350</t>
+          <t>66544</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>101496</t>
+          <t>101743</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>239995</t>
+          <t>240862</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>273672</t>
+          <t>272843</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>268712</t>
+          <t>268513</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>303539</t>
+          <t>303444</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>520382</t>
+          <t>518404</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>568736</t>
+          <t>569163</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,82 +720,82 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4568</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5135</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -1172,82 +1172,82 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>962</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4825</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4752</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>14,38%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>962</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -1511,72 +1511,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3292</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>801</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>801</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1624,47 +1624,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>26,46%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2338</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>369</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>406</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -1737,72 +1737,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3102</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6913</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -1850,72 +1850,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26270</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20086</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28946</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>24143</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20056</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26916</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>85,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>21874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>52982</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46777</t>
+          <t>39727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56876</t>
+          <t>49603</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -1963,74 +1963,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>23554</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>23554</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>23554</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>33052</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>33052</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>33052</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>78</t>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2080,47 +2080,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4885</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1138</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3941</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,22 +2155,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>891</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>860</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -2419,82 +2419,82 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2218</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>323</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -2532,107 +2532,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7761</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>9814</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>936</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -2645,72 +2645,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>6638</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>6021</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>383</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,32 +2720,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -2758,72 +2758,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8908</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4119</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>16014</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5578</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1814</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11813</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16030</t>
+          <t>14859</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26214</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2871,107 +2871,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5420</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4313</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3941</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>2261</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>6206</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>7078</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3753</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1540</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>8013</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -2984,72 +2984,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>15250</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>9350</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>23869</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6,38%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>11190</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>5710</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>18458</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>27486</t>
+          <t>26094</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18916</t>
+          <t>18491</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38071</t>
+          <t>35549</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -3097,72 +3097,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>27580</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>19521</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>41109</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>11,53%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>17436</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>10948</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>25519</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28732</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47084</t>
+          <t>25642</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>46167</t>
+          <t>45713</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34249</t>
+          <t>35255</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64317</t>
+          <t>61891</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -3210,72 +3210,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>178552</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>163701</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>190497</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>74,64%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>68,43%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>79,64%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>176881</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>165190</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>191144</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>81,63%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>76,23%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>192962</t>
+          <t>150813</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>175995</t>
+          <t>140668</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>206168</t>
+          <t>160005</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>369842</t>
+          <t>329365</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>348883</t>
+          <t>313136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>392450</t>
+          <t>344015</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -3323,74 +3323,74 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>191243</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>191243</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>191243</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>258230</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>258230</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>258230</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>643</t>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3440,47 +3440,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1882</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5796</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2361</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>389</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -3553,47 +3553,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3655</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>3880</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3666,82 +3666,82 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>4149</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -3779,72 +3779,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>2110</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>342</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>342</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3892,72 +3892,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>5349</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>960</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>7613</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -4118,72 +4118,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>4224</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2491</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>6828</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>770</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -4231,72 +4231,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>6856</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>1871</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>4783</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>8944</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>9149</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -4457,72 +4457,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>14527</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>9564</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>21097</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>23,85%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>17752</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>12206</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>24454</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>14,35%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>21337</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>32125</t>
+          <t>33112</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24291</t>
+          <t>25297</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>40276</t>
+          <t>41332</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -4570,72 +4570,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>61789</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>53570</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>68040</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>69,85%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>60,56%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>76,92%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>54236</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>46711</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>60717</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>63,78%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>54,93%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>71,4%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>66492</t>
+          <t>53853</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>57976</t>
+          <t>46664</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>73623</t>
+          <t>61117</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>120729</t>
+          <t>115642</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>109394</t>
+          <t>104626</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>131386</t>
+          <t>124914</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>71,82%</t>
         </is>
       </c>
     </row>
@@ -4683,74 +4683,74 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>85475</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>85475</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>85475</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>94867</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>94867</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>94867</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>257</t>
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,72 +4800,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>3815</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>9011</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>5533</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>363</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,22 +4875,22 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -4913,107 +4913,107 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>5978</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>1538</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>5028</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>3714</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>8345</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>3855</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>1432</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>8124</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -5026,82 +5026,82 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>4030</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>4863</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>342</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5189,49 +5189,49 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>2620</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -5252,72 +5252,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>3862</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>9542</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>5141</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -5365,72 +5365,72 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>3780</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>9340</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>3408</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>8836</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -5478,72 +5478,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>9780</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>5022</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>17711</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>8069</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>15978</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>21840</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>30769</t>
+          <t>27720</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -5591,72 +5591,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>3502</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>9161</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>1806</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>8749</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>3914</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>7894</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>4050</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>1382</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>9186</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>13933</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -5704,107 +5704,107 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>21121</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>13849</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>29605</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>15930</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>9821</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>23680</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>10039</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>23049</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>36769</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>27520</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>47489</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
           <t>4,18%</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>39365</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>28897</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>51151</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -5817,72 +5817,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>42107</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>32148</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>59117</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>8,98%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>38289</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>27886</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>48967</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>11,6%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>39583</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>32627</t>
+          <t>30341</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>60677</t>
+          <t>49277</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>81394</t>
+          <t>81691</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>66544</t>
+          <t>68121</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>101743</t>
+          <t>99760</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -5930,57 +5930,57 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>266611</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>249873</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>282316</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>350</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>255260</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>240862</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>272843</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>77,32%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>72,96%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>82,65%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224185</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>212332</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>236304</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>543554</t>
+          <t>490796</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>518404</t>
+          <t>469980</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>569163</t>
+          <t>510093</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -6043,74 +6043,74 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>467</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>300272</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>300272</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>300272</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>978</t>
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
